--- a/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_jlos_expanded_analysis.xlsx
+++ b/2 Output/Phase1_Baseline_Selected100_Observed/tables/phase1_baseline_jlos_expanded_analysis.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="120" uniqueCount="90">
   <si>
     <t>Advancing Justice Uganda - Phase 1 baseline expanded JLOS analysis</t>
   </si>
@@ -59,10 +59,10 @@
     <t>Knows cases requiring referral</t>
   </si>
   <si>
-    <t>Coordination with police</t>
-  </si>
-  <si>
-    <t>Coordination with courts</t>
+    <t>Perceived ease of police coordination</t>
+  </si>
+  <si>
+    <t>Perceived ease of court coordination</t>
   </si>
   <si>
     <t>Referral regularity</t>
@@ -89,6 +89,36 @@
     <t>item_id</t>
   </si>
   <si>
+    <t>indicator_with_n</t>
+  </si>
+  <si>
+    <t>Prior formal coordination (n=93)</t>
+  </si>
+  <si>
+    <t>Knows cases requiring referral (n=93)</t>
+  </si>
+  <si>
+    <t>Perceived ease of police coordination (n=91)</t>
+  </si>
+  <si>
+    <t>Perceived ease of court coordination (n=89)</t>
+  </si>
+  <si>
+    <t>Referral regularity (n=88)</t>
+  </si>
+  <si>
+    <t>Confidence knowing where to refer (n=93)</t>
+  </si>
+  <si>
+    <t>Confidence explaining referral (n=93)</t>
+  </si>
+  <si>
+    <t>Referral documentation (n=90)</t>
+  </si>
+  <si>
+    <t>Feedback after referral (n=90)</t>
+  </si>
+  <si>
     <t>reason</t>
   </si>
   <si>
@@ -179,7 +209,7 @@
     <t>stage</t>
   </si>
   <si>
-    <t>Police/court coordination</t>
+    <t>Perceived ease of police/court coordination</t>
   </si>
   <si>
     <t>Referral pathway confidence</t>
@@ -189,6 +219,21 @@
   </si>
   <si>
     <t>Verified referral record</t>
+  </si>
+  <si>
+    <t>stage_with_n</t>
+  </si>
+  <si>
+    <t>Perceived ease of police/court coordination (n=91)</t>
+  </si>
+  <si>
+    <t>Referral pathway confidence (n=93)</t>
+  </si>
+  <si>
+    <t>Documentation and feedback (n=91)</t>
+  </si>
+  <si>
+    <t>Verified referral record (n=63)</t>
   </si>
   <si>
     <t>canonical_district</t>
@@ -334,7 +379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -353,6 +398,9 @@
       <c r="E1" t="s">
         <v>22</v>
       </c>
+      <c r="F1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1">
@@ -362,13 +410,16 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>87.912087912087912</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
+        <v>88.172043010752688</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -379,13 +430,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>86.080585354632078</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
+        <v>86.021504623274652</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -396,13 +450,16 @@
         <v>13</v>
       </c>
       <c r="C4" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" s="1">
-        <v>74.438202247191015</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+        <v>74.72527472527473</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -413,13 +470,16 @@
         <v>14</v>
       </c>
       <c r="C5" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" s="1">
-        <v>69.827586206896555</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
+        <v>70.224719101123597</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -430,13 +490,16 @@
         <v>15</v>
       </c>
       <c r="C6" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" s="1">
-        <v>76.162790697674424</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>74.715909090909094</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -447,13 +510,16 @@
         <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1">
-        <v>59.340659340659343</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
+        <v>59.408602150537639</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -464,13 +530,16 @@
         <v>17</v>
       </c>
       <c r="C8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1">
-        <v>58.241758241758248</v>
-      </c>
-      <c r="E8" t="s">
-        <v>17</v>
+        <v>58.602150537634422</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -481,13 +550,16 @@
         <v>18</v>
       </c>
       <c r="C9" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1">
-        <v>45.170454545454547</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
+        <v>46.111111111111107</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -498,13 +570,16 @@
         <v>19</v>
       </c>
       <c r="C10" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" s="1">
-        <v>42.897727272727273</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
+        <v>42.222222222222221</v>
+      </c>
+      <c r="E10" s="1">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -521,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
         <v>20</v>
@@ -538,16 +613,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>83.516483516483518</v>
+        <v>83.870967741935488</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -555,16 +630,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>69.230769230769226</v>
+        <v>68.817204301075279</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
@@ -572,16 +647,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1">
-        <v>48.35164835164835</v>
+        <v>48.387096774193552</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -589,16 +664,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1">
-        <v>20.87912087912088</v>
+        <v>21.50537634408602</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -606,16 +681,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1">
-        <v>7.6923076923076934</v>
+        <v>8.6021505376344099</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -623,16 +698,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1">
-        <v>4.395604395604396</v>
+        <v>4.3010752688172049</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
@@ -640,16 +715,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9">
@@ -657,16 +732,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -683,7 +758,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C1" t="s">
         <v>20</v>
@@ -700,16 +775,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>51.648351648351657</v>
+        <v>51.612903225806449</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -717,16 +792,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>45.054945054945058</v>
+        <v>43.01075268817204</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
@@ -734,16 +809,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C4" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1">
-        <v>23.07692307692308</v>
+        <v>24.731182795698921</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -751,16 +826,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D5" s="1">
-        <v>18.681318681318679</v>
+        <v>18.27956989247312</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -768,16 +843,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1">
-        <v>4.395604395604396</v>
+        <v>4.3010752688172049</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -785,16 +860,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C7" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D7" s="1">
-        <v>3.296703296703297</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
@@ -802,16 +877,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C8" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="1">
-        <v>5.4945054945054954</v>
+        <v>5.3763440860215051</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -819,16 +894,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="1">
-        <v>3.296703296703297</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -836,16 +911,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C10" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1">
-        <v>1.098901098901099</v>
+        <v>1.075268817204301</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -853,16 +928,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1">
-        <v>1.098901098901099</v>
+        <v>1.075268817204301</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -870,16 +945,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C12" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" s="1">
-        <v>29.670329670329672</v>
+        <v>30.107526881720428</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +963,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,7 +971,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
         <v>20</v>
@@ -906,6 +981,9 @@
       </c>
       <c r="E1" t="s">
         <v>22</v>
+      </c>
+      <c r="F1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="2">
@@ -916,13 +994,16 @@
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>87.912087912087912</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
+        <v>88.172043010752688</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -933,13 +1014,16 @@
         <v>12</v>
       </c>
       <c r="C3" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D3" s="1">
-        <v>86.080585354632078</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
+        <v>86.021504623274652</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -947,16 +1031,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C4" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" s="1">
-        <v>72.471910112359552</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
+        <v>72.802197802197796</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
@@ -967,13 +1054,16 @@
         <v>15</v>
       </c>
       <c r="C5" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" s="1">
-        <v>76.162790697674424</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
+        <v>74.715909090909094</v>
+      </c>
+      <c r="E5" s="1">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -981,16 +1071,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D6" s="1">
-        <v>58.791208791208803</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
+        <v>59.005376344086017</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -998,16 +1091,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C7" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" s="1">
-        <v>43.960674157303373</v>
-      </c>
-      <c r="E7" t="s">
-        <v>55</v>
+        <v>44.093406593406591</v>
+      </c>
+      <c r="E7" s="1">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -1015,16 +1111,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C8" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D8" s="1">
-        <v>63.114754098360663</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
+        <v>63.095238095238088</v>
+      </c>
+      <c r="E8" s="1">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1038,107 +1137,107 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B1" t="s">
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="J1" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="K1" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="L1" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="M1" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="N1" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="O1" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="P1" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="1">
-        <v>0.875</v>
+        <v>0.87804877758026123</v>
       </c>
       <c r="D2" s="1">
-        <v>0.84444445371627808</v>
+        <v>0.84417343139648438</v>
       </c>
       <c r="E2" s="1">
-        <v>0.6875</v>
+        <v>0.69512195121951215</v>
       </c>
       <c r="F2" s="1">
-        <v>0.62179487179487181</v>
+        <v>0.63124999999999998</v>
       </c>
       <c r="G2" s="1">
-        <v>0.56874999999999998</v>
+        <v>0.56707317073170727</v>
       </c>
       <c r="H2" s="1">
-        <v>0.52500000000000002</v>
+        <v>0.52439024390243905</v>
       </c>
       <c r="I2" s="1">
-        <v>0.48125000000000001</v>
+        <v>0.48170731707317072</v>
       </c>
       <c r="J2" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.41875000000000001</v>
       </c>
       <c r="K2" s="1">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="L2" s="1">
         <v>0.66666666666666663</v>
       </c>
-      <c r="L2" s="1">
-        <v>0.67307692307692313</v>
-      </c>
       <c r="M2" s="1">
-        <v>0.5878596305847168</v>
+        <v>0.58910423517227173</v>
       </c>
       <c r="N2" s="1">
-        <v>2.2249999046325684</v>
+        <v>2.2195122241973877</v>
       </c>
       <c r="O2" s="1">
-        <v>1.7749999761581421</v>
+        <v>1.7804877758026123</v>
       </c>
       <c r="P2" s="1">
-        <v>0.22499999403953552</v>
+        <v>0.21951219439506531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="B3" s="1">
         <v>28</v>
@@ -1150,90 +1249,90 @@
         <v>0.875</v>
       </c>
       <c r="E3" s="1">
-        <v>0.83035714285714291</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="F3" s="1">
-        <v>0.7857142857142857</v>
+        <v>0.7767857142857143</v>
       </c>
       <c r="G3" s="1">
         <v>0.6607142857142857</v>
       </c>
       <c r="H3" s="1">
-        <v>0.6696428571428571</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="I3" s="1">
-        <v>0.4732142857142857</v>
+        <v>0.48214285714285715</v>
       </c>
       <c r="J3" s="1">
-        <v>0.5</v>
+        <v>0.48214285714285715</v>
       </c>
       <c r="K3" s="1">
-        <v>0.73076923076923073</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="L3" s="1">
-        <v>0.61764705882352944</v>
+        <v>0.59375</v>
       </c>
       <c r="M3" s="1">
-        <v>0.67375284433364868</v>
+        <v>0.66842049360275269</v>
       </c>
       <c r="N3" s="1">
-        <v>2.6428570747375488</v>
+        <v>2.7142856121063232</v>
       </c>
       <c r="O3" s="1">
-        <v>1.4642857313156128</v>
+        <v>1.3928571939468384</v>
       </c>
       <c r="P3" s="1">
-        <v>0.3928571343421936</v>
+        <v>0.4285714328289032</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B4" s="1">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1">
-        <v>0.78260868787765503</v>
+        <v>0.79166668653488159</v>
       </c>
       <c r="D4" s="1">
-        <v>0.87198066711425781</v>
+        <v>0.87037038803100586</v>
       </c>
       <c r="E4" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="F4" s="1">
         <v>0.73809523809523814</v>
       </c>
-      <c r="F4" s="1">
-        <v>0.72499999999999998</v>
-      </c>
       <c r="G4" s="1">
-        <v>0.55434782608695654</v>
+        <v>0.5625</v>
       </c>
       <c r="H4" s="1">
-        <v>0.57608695652173914</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="I4" s="1">
-        <v>0.36249999999999999</v>
+        <v>0.39285714285714285</v>
       </c>
       <c r="J4" s="1">
-        <v>0.35714285714285715</v>
+        <v>0.35227272727272729</v>
       </c>
       <c r="K4" s="1">
-        <v>0.80769230769230771</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="L4" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="M4" s="1">
-        <v>0.59110593795776367</v>
+        <v>0.59772652387619019</v>
       </c>
       <c r="N4" s="1">
-        <v>2.1739130020141602</v>
+        <v>2.1666667461395264</v>
       </c>
       <c r="O4" s="1">
-        <v>1.3478261232376099</v>
+        <v>1.375</v>
       </c>
       <c r="P4" s="1">
-        <v>0.30434781312942505</v>
+        <v>0.29166665673255921</v>
       </c>
     </row>
   </sheetData>
